--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MINNESOTA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MINNESOTA_2020.xlsx
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C78">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C91">
@@ -2533,7 +2533,7 @@
         <v>51</v>
       </c>
       <c r="D121">
-        <v>0.009313367421475529</v>
+        <v>0.009313367421475528</v>
       </c>
     </row>
     <row r="122">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C148">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C202">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C208">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C217">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C394">
@@ -8743,7 +8743,7 @@
         <v>51</v>
       </c>
       <c r="D466">
-        <v>0.009313367421475529</v>
+        <v>0.009313367421475528</v>
       </c>
     </row>
     <row r="467">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C501">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C526">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C628">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C663">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C711">
